--- a/GRAMMAR/7_19_07.xlsx
+++ b/GRAMMAR/7_19_07.xlsx
@@ -465,96 +465,88 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>我慢</t>
+          <t>ほこり</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>忍耐，忍受</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>がまん</t>
-        </is>
-      </c>
+          <t>灰尘；骄傲</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ものでしだ</t>
+          <t>納得</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>竟然</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>认可，认同</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>なっとく</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>多分</t>
+          <t>Vたきり〜ない</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>大概，或许</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>たぶん</t>
-        </is>
-      </c>
+          <t>自从...以后就再也（不）...</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ぐらい</t>
+          <t>〜によると〜ということでした</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(1)大约，左右(2)低程度，轻视语气</t>
+          <t>传闻</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>“ぐらいなら”与其…倒不如</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>じゅう</t>
+          <t>うらやましい</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>全，满</t>
+          <t>羡慕的</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -562,16 +554,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vたきり〜ない</t>
+          <t>ものでしだ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>自从...以后就再也（不）...</t>
+          <t>竟然</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -579,37 +571,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>とする</t>
+          <t>どころか</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>认为...，当作...</t>
+          <t>(接否定)别说...就连...</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>“とすると”假如</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ほこり</t>
+          <t>〜による</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>灰尘；骄傲</t>
+          <t>根据...；由于...</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -617,16 +605,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>〜ば〜ほど</t>
+          <t>としても</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>越...越...</t>
+          <t>即使...也...</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -634,37 +622,33 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>納得</t>
+          <t>あんな+N+も</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>认可，认同</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>なっとく</t>
-        </is>
-      </c>
+          <t>竟然有那样的…</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>あんな+N+も</t>
+          <t>てしまおう</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>竟然有那样的…</t>
+          <t>“てしまう”的意志型</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -672,16 +656,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vる+ところです</t>
+          <t>〜とする</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>将要…</t>
+          <t>(1)假如(2)决定(3)认为</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -693,12 +677,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>うらやましい</t>
+          <t>〜がVてある</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>羡慕的</t>
+          <t>结果状态存续</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -706,151 +690,155 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>きる</t>
+          <t>押し入れ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>彻底</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>壁橱</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>おしいれ</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>記事</t>
+          <t>からって</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>报道，记事</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>きじ</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>（口语）因为...就...</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>同“からといって”</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>〜がVてある</t>
+          <t>我慢</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>结果状态存续</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>忍耐，忍受</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>がまん</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>てしまおう</t>
+          <t>ぐらい</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>“てしまう”的意志型</t>
+          <t>(1)大约，左右(2)低程度，轻视语气</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>“ぐらいなら”与其…倒不如</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>〜と考えさせられる</t>
+          <t>きる</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>使役被动，情感上的情不自禁</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>〜とかんがえさせられる</t>
-        </is>
-      </c>
+          <t>彻底</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>知恵</t>
+          <t>じゅう</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>智慧，主意</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ちえ</t>
-        </is>
-      </c>
+          <t>全，满</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>からって</t>
+          <t>どうか〜ように+祈る/願う/期待する</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>（口语）因为...就...</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>同“からといって”</t>
-        </is>
-      </c>
+          <t>祈祷/祝愿/期待能...</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>どうか〜ように+いのる/ねがう/きたいする</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>〜によると〜ということでした</t>
+          <t>つまり</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>传闻</t>
+          <t>总之，也就是</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -862,12 +850,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>〜による</t>
+          <t>〜ば〜ほど</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>根据...；由于...</t>
+          <t>越...越...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -875,59 +863,63 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>てたまらない</t>
+          <t>とする</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>...得不得了，非常...</t>
+          <t>认为...，当作...</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>“とすると”假如</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>そういう</t>
+          <t>記事</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>那样的</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>“ああいう”那种的(不好的情况)</t>
-        </is>
-      </c>
+          <t>报道，记事</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>きじ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>何度</t>
+          <t>多分</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>几次，多少次</t>
+          <t>大概，或许</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>なんど</t>
+          <t>たぶん</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -938,12 +930,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>としても</t>
+          <t>Vる+ところです</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>即使...也...</t>
+          <t>将要…</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -955,19 +947,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>どうか〜ように+祈る/願う/期待する</t>
+          <t>てたまらない</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>祈祷/祝愿/期待能...</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>どうか〜ように+いのる/ねがう/きたいする</t>
-        </is>
-      </c>
+          <t>...得不得了，非常...</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -976,29 +964,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>どころか</t>
+          <t>知恵</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(接否定)别说...就连...</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>智慧，主意</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ちえ</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ものなら</t>
+          <t>しかも</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>如果能...的话（希望能实现）</t>
+          <t>而且</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1006,37 +998,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>時代に</t>
+          <t>〜と考えさせられる</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>在...时代</t>
+          <t>使役被动，情感上的情不自禁</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>じだいに</t>
+          <t>〜とかんがえさせられる</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>すぐに</t>
+          <t>させられます</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>马上，立刻</t>
+          <t>被迫做...，自然而然...（使役被动形）</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1044,41 +1036,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>だらけ</t>
+          <t>N+きり</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>满是...（多指负面事物）</t>
+          <t>只有...，仅...</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>“V+きり”…完;…尽</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>N+きり</t>
+          <t>プロ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>只有...，仅...</t>
+          <t>专业人士</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>“V+きり”…完;…尽</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1086,53 +1078,57 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>プロ</t>
+          <t>気分</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>专业人士</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>心情，气氛</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>きぶん</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>押し入れ</t>
+          <t>〜てみたら</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>壁橱</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>おしいれ</t>
-        </is>
-      </c>
+          <t>尝试发现…</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>つまり</t>
+          <t>時代に</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>总之，也就是</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>在...时代</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>じだいに</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1141,12 +1137,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>〜とする</t>
+          <t>だらけ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(1)假如(2)决定(3)认为</t>
+          <t>满是...（多指负面事物）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1154,16 +1150,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>しかも</t>
+          <t>すぐに</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>而且</t>
+          <t>马上，立刻</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1175,12 +1171,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>〜てみたら</t>
+          <t>ものなら</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>尝试发现…</t>
+          <t>如果能...的话（希望能实现）</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1192,17 +1188,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>気分</t>
+          <t>何度</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>心情，气氛</t>
+          <t>几次，多少次</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>きぶん</t>
+          <t>なんど</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1213,16 +1209,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>させられます</t>
+          <t>そういう</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>被迫做...，自然而然...（使役被动形）</t>
+          <t>那样的</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>“ああいう”那种的(不好的情况)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GRAMMAR/7_19_07.xlsx
+++ b/GRAMMAR/7_19_07.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -465,33 +465,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>〜がVてある</t>
+          <t>我慢</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>结果状态存续</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>忍耐，忍受</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>がまん</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vる+ところです</t>
+          <t>ものでしだ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>将要…</t>
+          <t>竟然</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -499,58 +503,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>からって</t>
+          <t>多分</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>（口语）因为...就...</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>同“からといって”</t>
-        </is>
-      </c>
+          <t>大概，或许</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>たぶん</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>〜とする</t>
+          <t>ぐらい</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(1)假如(2)决定(3)认为</t>
+          <t>(1)大约，左右(2)低程度，轻视语气</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>“とすると”假如</t>
+          <t>“ぐらいなら”与其…倒不如</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>あんな+N+も</t>
+          <t>じゅう</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>竟然有那样的…</t>
+          <t>全，满</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -558,7 +562,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -575,24 +579,24 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>納得</t>
+          <t>とする</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>认可，认同</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>なっとく</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>认为...，当作...</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>“とすると”假如</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -613,16 +617,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>てしまおう</t>
+          <t>〜ば〜ほど</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>“てしまう”的意志型</t>
+          <t>越...越...</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -634,17 +638,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>我慢</t>
+          <t>納得</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>忍耐，忍受</t>
+          <t>认可，认同</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>がまん</t>
+          <t>なっとく</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -655,12 +659,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>〜による</t>
+          <t>あんな+N+も</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>根据...；由于...</t>
+          <t>竟然有那样的…</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -672,40 +676,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>知恵</t>
+          <t>Vる+ところです</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>智慧，主意</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ちえ</t>
-        </is>
-      </c>
+          <t>将要…</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>〜と考えさせられる</t>
+          <t>うらやましい</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>使役被动，情感上的情不自禁</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>〜とかんがえさせられる</t>
-        </is>
-      </c>
+          <t>羡慕的</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -714,19 +710,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>押し入れ</t>
+          <t>きる</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>壁橱</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>おしいれ</t>
-        </is>
-      </c>
+          <t>彻底</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -735,20 +727,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N+きり</t>
+          <t>記事</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>只有...，仅...</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>“V+きり”…完;…尽</t>
-        </is>
-      </c>
+          <t>报道，记事</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>きじ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -756,12 +748,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ものでしだ</t>
+          <t>〜がVてある</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>竟然</t>
+          <t>结果状态存续</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -773,12 +765,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>〜によると〜ということでした</t>
+          <t>てしまおう</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>传闻</t>
+          <t>“てしまう”的意志型</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -790,15 +782,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>てたまらない</t>
+          <t>〜と考えさせられる</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>...得不得了，非常...</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>使役被动，情感上的情不自禁</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>〜とかんがえさせられる</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -807,20 +803,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ぐらい</t>
+          <t>知恵</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(1)大约，左右(2)低程度，轻视语气</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>“ぐらいなら”与其…倒不如</t>
-        </is>
-      </c>
+          <t>智慧，主意</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ちえ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -828,29 +824,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>うらやましい</t>
+          <t>からって</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>羡慕的</t>
+          <t>（口语）因为...就...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>同“からといって”</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>〜ば〜ほど</t>
+          <t>〜によると〜ということでした</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>越...越...</t>
+          <t>传闻</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -862,33 +862,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>多分</t>
+          <t>〜による</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>大概，或许</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>たぶん</t>
-        </is>
-      </c>
+          <t>根据...；由于...</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>きる</t>
+          <t>てたまらない</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>彻底</t>
+          <t>...得不得了，非常...</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -896,54 +892,58 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>記事</t>
+          <t>そういう</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>报道，记事</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>きじ</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>那样的</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>“ああいう”那种的(不好的情况)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>じゅう</t>
+          <t>何度</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>全，满</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>几次，多少次</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>なんど</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>つまり</t>
+          <t>としても</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>总之，也就是</t>
+          <t>即使...也...</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -951,37 +951,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>気分</t>
+          <t>どうか〜ように+祈る/願う/期待する</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>心情，气氛</t>
+          <t>祈祷/祝愿/期待能...</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>きぶん</t>
+          <t>どうか〜ように+いのる/ねがう/きたいする</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>〜てみたら</t>
+          <t>どころか</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>尝试发现…</t>
+          <t>(接否定)别说...就连...</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>しかも</t>
+          <t>ものなら</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>而且</t>
+          <t>如果能...的话（希望能实现）</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1010,15 +1010,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>プロ</t>
+          <t>時代に</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>专业人士</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>在...时代</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>じだいに</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1027,19 +1031,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>時代に</t>
+          <t>すぐに</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>在...时代</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>じだいに</t>
-        </is>
-      </c>
+          <t>马上，立刻</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1061,24 +1061,24 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>どうか〜ように+祈る/願う/期待する</t>
+          <t>N+きり</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>祈祷/祝愿/期待能...</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>どうか〜ように+いのる/ねがう/きたいする</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>只有...，仅...</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>“V+きり”…完;…尽</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ものなら</t>
+          <t>プロ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>如果能...的话（希望能实现）</t>
+          <t>专业人士</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1099,33 +1099,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>どころか</t>
+          <t>押し入れ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(接否定)别说...就连...</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>壁橱</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>おしいれ</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>としても</t>
+          <t>つまり</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>即使...也...</t>
+          <t>总之，也就是</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1137,41 +1141,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>何度</t>
+          <t>〜とする</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>几次，多少次</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>なんど</t>
-        </is>
-      </c>
+          <t>(1)假如(2)决定(3)认为</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>そういう</t>
+          <t>しかも</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>那样的</t>
+          <t>而且</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>“ああいう”那种的(不好的情况)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1179,12 +1175,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>すぐに</t>
+          <t>〜てみたら</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>马上，立刻</t>
+          <t>尝试发现…</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1196,16 +1192,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>気分</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>心情，气氛</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>きぶん</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>させられます</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>被迫做...，自然而然...（使役被动形）</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GRAMMAR/7_19_07.xlsx
+++ b/GRAMMAR/7_19_07.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -462,6 +462,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -479,10 +484,15 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -496,6 +506,11 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -517,6 +532,11 @@
           <t>同“からといって”</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -538,10 +558,15 @@
           <t>“とすると”假如</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -555,6 +580,11 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -572,6 +602,11 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -593,6 +628,11 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -610,10 +650,15 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -627,6 +672,11 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -648,6 +698,11 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -665,6 +720,11 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -686,6 +746,11 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -707,6 +772,11 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -728,10 +798,15 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -749,10 +824,15 @@
           <t>“V+きり”…完;…尽</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -766,6 +846,11 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -783,6 +868,11 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -800,6 +890,11 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -821,6 +916,11 @@
           <t>“ぐらいなら”与其…倒不如</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -838,6 +938,11 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -855,10 +960,15 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -876,6 +986,11 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -893,6 +1008,11 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -914,6 +1034,11 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -931,6 +1056,11 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -948,6 +1078,11 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -969,6 +1104,11 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -986,6 +1126,11 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1003,6 +1148,11 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1020,6 +1170,11 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1041,6 +1196,11 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1058,6 +1218,11 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1079,6 +1244,11 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1096,6 +1266,11 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1113,10 +1288,15 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1130,6 +1310,11 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1151,6 +1336,11 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1172,6 +1362,11 @@
           <t>“ああいう”那种的(不好的情况)</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1189,6 +1384,11 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1206,6 +1406,11 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
